--- a/MCMI_III_Scoring_System/MCMI_III_Scoring_Tool.xlsx
+++ b/MCMI_III_Scoring_System/MCMI_III_Scoring_Tool.xlsx
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="C7">
-        <f>IF(AND(DATA!B6&lt;&gt;"",DATA!B152&lt;&gt;"",DATA!B6&lt;&gt;DATA!B152),1,0)+IF(AND(DATA!B13&lt;&gt;"",DATA!B168&lt;&gt;"",DATA!B13&lt;&gt;DATA!B168),1,0)+IF(AND(DATA!B17&lt;&gt;"",DATA!B97&lt;&gt;"",DATA!B17&lt;&gt;DATA!B97),1,0)+IF(AND(DATA!B18&lt;&gt;"",DATA!B64&lt;&gt;"",DATA!B18&lt;&gt;DATA!B64),1,0)+IF(AND(DATA!B22&lt;&gt;"",DATA!B153&lt;&gt;"",DATA!B22&lt;&gt;DATA!B153),1,0)+IF(AND(DATA!B28&lt;&gt;"",DATA!B133&lt;&gt;"",DATA!B28&lt;&gt;DATA!B133),1,0)+IF(AND(DATA!B42&lt;&gt;"",DATA!B159&lt;&gt;"",DATA!B42&lt;&gt;DATA!B159),1,0)+IF(AND(DATA!B45&lt;&gt;"",DATA!B96&lt;&gt;"",DATA!B45&lt;&gt;DATA!B96),1,0)+IF(AND(DATA!B52&lt;&gt;"",DATA!B155&lt;&gt;"",DATA!B52&lt;&gt;DATA!B155),1,0)+IF(AND(DATA!B60&lt;&gt;"",DATA!B100&lt;&gt;"",DATA!B60&lt;&gt;DATA!B100),1,0)+IF(AND(DATA!B63&lt;&gt;"",DATA!B108&lt;&gt;"",DATA!B63&lt;&gt;DATA!B108),1,0)+IF(AND(DATA!B65&lt;&gt;"",DATA!B114&lt;&gt;"",DATA!B65&lt;&gt;DATA!B114),1,0)+IF(AND(DATA!B69&lt;&gt;"",DATA!B120&lt;&gt;"",DATA!B69&lt;&gt;DATA!B120),1,0)+IF(AND(DATA!B70&lt;&gt;"",DATA!B158&lt;&gt;"",DATA!B70&lt;&gt;DATA!B158),1,0)+IF(AND(DATA!B73&lt;&gt;"",DATA!B122&lt;&gt;"",DATA!B73&lt;&gt;DATA!B122),1,0)+IF(AND(DATA!B76&lt;&gt;"",DATA!B123&lt;&gt;"",DATA!B76&lt;&gt;DATA!B123),1,0)+IF(AND(DATA!B78&lt;&gt;"",DATA!B163&lt;&gt;"",DATA!B78&lt;&gt;DATA!B163),1,0)+IF(AND(DATA!B82&lt;&gt;"",DATA!B128&lt;&gt;"",DATA!B82&lt;&gt;DATA!B128),1,0)+IF(AND(DATA!B83&lt;&gt;"",DATA!B169&lt;&gt;"",DATA!B83&lt;&gt;DATA!B169),1,0)+IF(AND(DATA!B87&lt;&gt;"",DATA!B130&lt;&gt;"",DATA!B87&lt;&gt;DATA!B130),1,0)+IF(AND(DATA!B89&lt;&gt;"",DATA!B131&lt;&gt;"",DATA!B89&lt;&gt;DATA!B131),1,0)+IF(AND(DATA!B92&lt;&gt;"",DATA!B137&lt;&gt;"",DATA!B92&lt;&gt;DATA!B137),1,0)+IF(AND(DATA!B94&lt;&gt;"",DATA!B172&lt;&gt;"",DATA!B94&lt;&gt;DATA!B172),1,0)+IF(AND(DATA!B101&lt;&gt;"",DATA!B141&lt;&gt;"",DATA!B101&lt;&gt;DATA!B141),1,0)+IF(AND(DATA!B104&lt;&gt;"",DATA!B145&lt;&gt;"",DATA!B104&lt;&gt;DATA!B145),1,0)+IF(AND(DATA!B105&lt;&gt;"",DATA!B146&lt;&gt;"",DATA!B105&lt;&gt;DATA!B146),1,0)+IF(AND(DATA!B107&lt;&gt;"",DATA!B147&lt;&gt;"",DATA!B107&lt;&gt;DATA!B147),1,0)+IF(AND(DATA!B111&lt;&gt;"",DATA!B150&lt;&gt;"",DATA!B111&lt;&gt;DATA!B150),1,0)+IF(AND(DATA!B115&lt;&gt;"",DATA!B154&lt;&gt;"",DATA!B115&lt;&gt;DATA!B154),1,0)+IF(AND(DATA!B119&lt;&gt;"",DATA!B156&lt;&gt;"",DATA!B119&lt;&gt;DATA!B156),1,0)+IF(AND(DATA!B5&lt;&gt;"",DATA!B91&lt;&gt;"",DATA!B5&lt;&gt;DATA!B91),1,0)+IF(AND(DATA!B8&lt;&gt;"",DATA!B80&lt;&gt;"",DATA!B8&lt;&gt;DATA!B80),1,0)+IF(AND(DATA!B14&lt;&gt;"",DATA!B57&lt;&gt;"",DATA!B14&lt;&gt;DATA!B57),1,0)+IF(AND(DATA!B23&lt;&gt;"",DATA!B140&lt;&gt;"",DATA!B23&lt;&gt;DATA!B140),1,0)+IF(AND(DATA!B25&lt;&gt;"",DATA!B124&lt;&gt;"",DATA!B25&lt;&gt;DATA!B124),1,0)+IF(AND(DATA!B34&lt;&gt;"",DATA!B164&lt;&gt;"",DATA!B34&lt;&gt;DATA!B164),1,0)+IF(AND(DATA!B40&lt;&gt;"",DATA!B66&lt;&gt;"",DATA!B40&lt;&gt;DATA!B66),1,0)+IF(AND(DATA!B43&lt;&gt;"",DATA!B167&lt;&gt;"",DATA!B43&lt;&gt;DATA!B167),1,0)+IF(AND(DATA!B44&lt;&gt;"",DATA!B142&lt;&gt;"",DATA!B44&lt;&gt;DATA!B142),1,0)+IF(AND(DATA!B48&lt;&gt;"",DATA!B84&lt;&gt;"",DATA!B48&lt;&gt;DATA!B84),1,0)+IF(AND(DATA!B49&lt;&gt;"",DATA!B81&lt;&gt;"",DATA!B49&lt;&gt;DATA!B81),1,0)+IF(AND(DATA!B54&lt;&gt;"",DATA!B161&lt;&gt;"",DATA!B54&lt;&gt;DATA!B161),1,0)+IF(AND(DATA!B56&lt;&gt;"",DATA!B138&lt;&gt;"",DATA!B56&lt;&gt;DATA!B138),1,0)+IF(AND(DATA!B58&lt;&gt;"",DATA!B175&lt;&gt;"",DATA!B58&lt;&gt;DATA!B175),1,0)</f>
+        <f>IF(AND(DATA!B6="T",DATA!B152="T"),1,0)+IF(AND(DATA!B13="T",DATA!B168="T"),1,0)+IF(AND(DATA!B17="T",DATA!B97="T"),1,0)+IF(AND(DATA!B18="T",DATA!B64="T"),1,0)+IF(AND(DATA!B22="T",DATA!B153="T"),1,0)+IF(AND(DATA!B28="T",DATA!B133="T"),1,0)+IF(AND(DATA!B42="T",DATA!B159="T"),1,0)+IF(AND(DATA!B45="T",DATA!B96="T"),1,0)+IF(AND(DATA!B52="T",DATA!B155="T"),1,0)+IF(AND(DATA!B60="T",DATA!B100="T"),1,0)+IF(AND(DATA!B63="T",DATA!B108="T"),1,0)+IF(AND(DATA!B65="T",DATA!B114="T"),1,0)+IF(AND(DATA!B69="T",DATA!B120="T"),1,0)+IF(AND(DATA!B70="T",DATA!B158="T"),1,0)+IF(AND(DATA!B73="T",DATA!B122="T"),1,0)+IF(AND(DATA!B76="T",DATA!B123="T"),1,0)+IF(AND(DATA!B78="T",DATA!B163="T"),1,0)+IF(AND(DATA!B82="T",DATA!B128="T"),1,0)+IF(AND(DATA!B83="T",DATA!B169="T"),1,0)+IF(AND(DATA!B87="T",DATA!B130="T"),1,0)+IF(AND(DATA!B89="T",DATA!B131="T"),1,0)+IF(AND(DATA!B92="T",DATA!B137="T"),1,0)+IF(AND(DATA!B94="T",DATA!B172="T"),1,0)+IF(AND(DATA!B101="T",DATA!B141="T"),1,0)+IF(AND(DATA!B104="T",DATA!B145="T"),1,0)+IF(AND(DATA!B105="T",DATA!B146="T"),1,0)+IF(AND(DATA!B107="T",DATA!B147="T"),1,0)+IF(AND(DATA!B111="T",DATA!B150="T"),1,0)+IF(AND(DATA!B115="T",DATA!B154="T"),1,0)+IF(AND(DATA!B119="T",DATA!B156="T"),1,0)+IF(AND(DATA!B5="T",DATA!B91="T"),1,0)+IF(AND(DATA!B8="T",DATA!B80="T"),1,0)+IF(AND(DATA!B14="T",DATA!B57="T"),1,0)+IF(AND(DATA!B23="T",DATA!B140="T"),1,0)+IF(AND(DATA!B25="T",DATA!B124="T"),1,0)+IF(AND(DATA!B34="T",DATA!B164="T"),1,0)+IF(AND(DATA!B40="T",DATA!B66="T"),1,0)+IF(AND(DATA!B43="T",DATA!B167="T"),1,0)+IF(AND(DATA!B44="T",DATA!B142="T"),1,0)+IF(AND(DATA!B48="T",DATA!B84="T"),1,0)+IF(AND(DATA!B49="T",DATA!B81="T"),1,0)+IF(AND(DATA!B54="T",DATA!B161="T"),1,0)+IF(AND(DATA!B56="T",DATA!B138="T"),1,0)+IF(AND(DATA!B58="T",DATA!B175="T"),1,0)</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
